--- a/수행평가_구글시트_빈템플릿.xlsx
+++ b/수행평가_구글시트_빈템플릿.xlsx
@@ -174,6 +174,7 @@
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -197,8 +198,18 @@
           <t>그룹</t>
         </is>
       </c>
-    </row>
-  </sheetData>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="영역 상태" error="완료, 이번 수행, 예정 중에서 골라주세요." sqref="E2:E1000">
+      <formula1>"완료,이번 수행,예정"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
@@ -244,8 +255,7 @@
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -271,11 +281,6 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>메모</t>
         </is>
       </c>

--- a/수행평가_구글시트_빈템플릿.xlsx
+++ b/수행평가_구글시트_빈템플릿.xlsx
@@ -6,7 +6,7 @@
     <sheet name="과목" sheetId="2" r:id="rId2"/>
     <sheet name="영역" sheetId="3" r:id="rId3"/>
     <sheet name="명단" sheetId="4" r:id="rId4"/>
-    <sheet name="진행상태" sheetId="5" r:id="rId5"/>
+    <sheet name="영역메모" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>

--- a/수행평가_구글시트_빈템플릿.xlsx
+++ b/수행평가_구글시트_빈템플릿.xlsx
@@ -139,6 +139,7 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -160,6 +161,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>개별수강생</t>
         </is>
       </c>
     </row>

--- a/수행평가_구글시트_빈템플릿.xlsx
+++ b/수행평가_구글시트_빈템플릿.xlsx
@@ -139,7 +139,6 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -161,11 +160,6 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>개별수강생</t>
         </is>
       </c>
     </row>

--- a/수행평가_구글시트_빈템플릿.xlsx
+++ b/수행평가_구글시트_빈템플릿.xlsx
@@ -175,6 +175,7 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -203,11 +204,19 @@
           <t>상태</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>급간</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="영역 상태" error="완료, 이번 수행, 예정 중에서 골라주세요." sqref="E2:E1000">
       <formula1>"완료,이번 수행,예정"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="급간" error="1~10 중에서 골라주세요. 비워 두면 점수를 직접 입력해요." sqref="F2:F1000">
+      <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
